--- a/Deliverables/BOM/Digikey_BOM.xlsx
+++ b/Deliverables/BOM/Digikey_BOM.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="229">
   <si>
     <t>Description</t>
   </si>
@@ -663,6 +663,67 @@
   </si>
   <si>
     <t>RMCF0603FG49K9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RL73H3AR18FTE
+</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panasonic </t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>8-SOIC</t>
+  </si>
+  <si>
+    <t>Quest Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinamic </t>
+  </si>
+  <si>
+    <t>onsemi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infineon </t>
+  </si>
+  <si>
+    <t>Avnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-TSSOP
+</t>
+  </si>
+  <si>
+    <t>Alibaba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amphenol </t>
+  </si>
+  <si>
+    <t>Wurth Elektronik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QBLP595-IG-2897
+</t>
+  </si>
+  <si>
+    <t>QT Brightek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Würth Elektronik</t>
+  </si>
+  <si>
+    <t>Ind 0603</t>
   </si>
 </sst>
 </file>
@@ -939,7 +1000,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -996,24 +1057,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1024,8 +1067,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1033,32 +1082,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1355,30 +1419,30 @@
     <col min="9" max="9" width="8" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19.5703125" customWidth="1"/>
     <col min="15" max="15" width="48.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="22"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1431,19 +1495,19 @@
       <c r="A3" s="13">
         <v>1</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="35" t="s">
+      <c r="D3" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="14" t="s">
         <v>48</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -1452,19 +1516,19 @@
       <c r="H3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="38">
+      <c r="J3" s="12">
         <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>2000</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="39">
+      <c r="M3" s="26">
         <v>0.14152000000000001</v>
       </c>
       <c r="N3" s="8">
@@ -1475,45 +1539,45 @@
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="33" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="12">
         <v>26</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="39">
         <v>10400</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="41">
         <v>3.2744230769230803E-2</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="42">
         <f t="shared" ref="N4:N46" si="0">M4*K4</f>
         <v>340.54000000000036</v>
       </c>
@@ -1525,17 +1589,17 @@
       <c r="A5" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="14" t="s">
         <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -1544,19 +1608,19 @@
       <c r="H5" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="12">
         <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>400</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="39">
+      <c r="M5" s="26">
         <v>0.15870000000000001</v>
       </c>
       <c r="N5" s="8">
@@ -1571,17 +1635,17 @@
       <c r="A6" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="14" t="s">
         <v>58</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1590,19 +1654,19 @@
       <c r="H6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="12">
         <v>4</v>
       </c>
       <c r="K6" s="5">
         <v>1600</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M6" s="39">
+      <c r="M6" s="26">
         <v>9.0319999999999998E-2</v>
       </c>
       <c r="N6" s="8">
@@ -1613,21 +1677,21 @@
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="14" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1636,19 +1700,19 @@
       <c r="H7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="12">
         <v>12</v>
       </c>
       <c r="K7" s="5">
         <v>4800</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="39">
+      <c r="M7" s="26">
         <v>1.0987500000000001E-2</v>
       </c>
       <c r="N7" s="8">
@@ -1663,17 +1727,17 @@
       <c r="A8" s="13">
         <v>6</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="14" t="s">
         <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1682,19 +1746,19 @@
       <c r="H8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="12">
         <v>3</v>
       </c>
       <c r="K8" s="5">
         <v>1200</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="39">
+      <c r="M8" s="26">
         <v>2.0830000000000001E-2</v>
       </c>
       <c r="N8" s="8">
@@ -1709,17 +1773,17 @@
       <c r="A9" s="13">
         <v>7</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="14" t="s">
         <v>67</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1728,19 +1792,19 @@
       <c r="H9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="12">
         <v>1</v>
       </c>
       <c r="K9" s="5">
         <v>400</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="39">
+      <c r="M9" s="26">
         <v>0.1024</v>
       </c>
       <c r="N9" s="8">
@@ -1751,36 +1815,38 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>8</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="33"/>
+      <c r="C10" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35" t="s">
+      <c r="E10" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>70</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="12">
         <v>1</v>
       </c>
       <c r="K10" s="5">
         <v>400</v>
       </c>
       <c r="L10" s="6"/>
-      <c r="M10" s="39"/>
+      <c r="M10" s="26"/>
       <c r="N10" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1789,34 +1855,36 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>9</v>
       </c>
-      <c r="B11" s="24"/>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="33"/>
+      <c r="C11" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35" t="s">
+      <c r="E11" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>73</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="12">
         <v>2</v>
       </c>
       <c r="K11" s="5">
         <v>800</v>
       </c>
       <c r="L11" s="6"/>
-      <c r="M11" s="39"/>
+      <c r="M11" s="26"/>
       <c r="N11" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1829,30 +1897,32 @@
       <c r="A12" s="13">
         <v>10</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="33" t="s">
+      <c r="B12" s="33"/>
+      <c r="C12" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35" t="s">
+      <c r="E12" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="11"/>
-      <c r="I12" s="35" t="s">
+      <c r="I12" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12" s="12">
         <v>1</v>
       </c>
       <c r="K12" s="5">
         <v>400</v>
       </c>
       <c r="L12" s="6"/>
-      <c r="M12" s="39"/>
+      <c r="M12" s="26"/>
       <c r="N12" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1861,41 +1931,41 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:17" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>11</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="33" t="s">
+      <c r="B13" s="33"/>
+      <c r="C13" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="14" t="s">
         <v>80</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="11"/>
-      <c r="I13" s="35" t="s">
+      <c r="I13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13" s="12">
         <v>1</v>
       </c>
       <c r="K13" s="5">
         <v>400</v>
       </c>
       <c r="L13" s="6"/>
-      <c r="M13" s="39"/>
+      <c r="M13" s="26"/>
       <c r="N13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O13" s="26"/>
+      <c r="O13" s="20"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
@@ -1903,17 +1973,17 @@
       <c r="A14" s="13">
         <v>12</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="40" t="s">
+      <c r="B14" s="34"/>
+      <c r="C14" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="11" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1922,19 +1992,19 @@
       <c r="H14" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="I14" s="35" t="s">
+      <c r="I14" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="12">
         <v>1</v>
       </c>
       <c r="K14" s="5">
         <v>400</v>
       </c>
-      <c r="L14" s="15" t="s">
+      <c r="L14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="39">
+      <c r="M14" s="26">
         <v>0.35720000000000002</v>
       </c>
       <c r="N14" s="8">
@@ -1945,23 +2015,23 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>13</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="14" t="s">
         <v>86</v>
       </c>
       <c r="G15" s="3"/>
@@ -1969,14 +2039,14 @@
       <c r="I15" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J15" s="38">
+      <c r="J15" s="12">
         <v>1</v>
       </c>
       <c r="K15" s="5">
         <v>400</v>
       </c>
       <c r="L15" s="6"/>
-      <c r="M15" s="39"/>
+      <c r="M15" s="26"/>
       <c r="N15" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1989,81 +2059,81 @@
       <c r="A16" s="13">
         <v>14</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="40" t="s">
+      <c r="B16" s="33"/>
+      <c r="C16" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="14" t="s">
         <v>88</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="H16" s="27" t="s">
+      <c r="H16" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16" s="12">
         <v>1</v>
       </c>
       <c r="K16" s="16">
         <v>400</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M16" s="39">
+      <c r="M16" s="26">
         <v>0.30769999999999997</v>
       </c>
       <c r="N16" s="8">
         <f t="shared" si="0"/>
         <v>123.07999999999998</v>
       </c>
-      <c r="O16" s="28"/>
+      <c r="O16" s="22"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>15</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="33" t="s">
+      <c r="B17" s="34"/>
+      <c r="C17" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35" t="s">
+      <c r="E17" s="14"/>
+      <c r="F17" s="14" t="s">
         <v>91</v>
       </c>
       <c r="G17" s="14"/>
-      <c r="H17" s="27"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J17" s="38">
+      <c r="J17" s="12">
         <v>1</v>
       </c>
       <c r="K17" s="16">
         <v>400</v>
       </c>
       <c r="L17" s="6"/>
-      <c r="M17" s="39"/>
+      <c r="M17" s="26"/>
       <c r="N17" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O17" s="28"/>
+      <c r="O17" s="22"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
@@ -2074,16 +2144,16 @@
       <c r="B18" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="14" t="s">
         <v>94</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -2101,89 +2171,111 @@
       <c r="K18" s="5">
         <v>400</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="L18" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="M18" s="39">
+      <c r="M18" s="26">
         <v>0.59919999999999995</v>
       </c>
       <c r="N18" s="8">
         <f t="shared" si="0"/>
         <v>239.67999999999998</v>
       </c>
-      <c r="O18" s="26"/>
+      <c r="O18" s="20"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>17</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="I19" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J19" s="3"/>
+      <c r="J19" s="3">
+        <v>2</v>
+      </c>
       <c r="K19" s="5">
         <v>800</v>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="39"/>
+      <c r="L19" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="26">
+        <v>0.11278000000000001</v>
+      </c>
       <c r="N19" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="26"/>
+        <v>90.224000000000004</v>
+      </c>
+      <c r="O19" s="20"/>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
     </row>
-    <row r="20" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>18</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35" t="s">
+      <c r="E20" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
+      <c r="G20" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H20" s="4">
+        <v>742792651</v>
+      </c>
       <c r="I20" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="J20" s="3"/>
+      <c r="J20" s="3">
+        <v>5</v>
+      </c>
       <c r="K20" s="5">
         <v>2000</v>
       </c>
-      <c r="L20" s="6"/>
-      <c r="M20" s="39"/>
+      <c r="L20" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="26">
+        <v>0.13400000000000001</v>
+      </c>
       <c r="N20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="O20" s="4"/>
       <c r="P20" s="2"/>
@@ -2193,17 +2285,17 @@
       <c r="A21" s="13">
         <v>19</v>
       </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="33" t="s">
+      <c r="B21" s="33"/>
+      <c r="C21" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="14" t="s">
         <v>104</v>
       </c>
       <c r="G21" s="3"/>
@@ -2216,7 +2308,7 @@
         <v>400</v>
       </c>
       <c r="L21" s="6"/>
-      <c r="M21" s="39"/>
+      <c r="M21" s="26"/>
       <c r="N21" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2229,19 +2321,25 @@
       <c r="A22" s="13">
         <v>20</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="33" t="s">
+      <c r="B22" s="34"/>
+      <c r="C22" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="35" t="s">
+      <c r="D22" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35" t="s">
+      <c r="E22" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="I22" s="3" t="s">
         <v>179</v>
       </c>
@@ -2251,10 +2349,10 @@
       <c r="K22" s="5">
         <v>400</v>
       </c>
-      <c r="L22" s="15" t="s">
+      <c r="L22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="39">
+      <c r="M22" s="26">
         <v>0.94099999999999995</v>
       </c>
       <c r="N22" s="8">
@@ -2265,23 +2363,23 @@
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>21</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="D23" s="35" t="s">
+      <c r="D23" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="14" t="s">
         <v>112</v>
       </c>
       <c r="G23" s="3" t="s">
@@ -2290,19 +2388,19 @@
       <c r="H23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="12">
         <v>15</v>
       </c>
       <c r="K23" s="12">
         <v>600</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M23" s="39">
+      <c r="M23" s="26">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="N23" s="8">
@@ -2317,17 +2415,17 @@
       <c r="A24" s="13">
         <v>22</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="33" t="s">
+      <c r="B24" s="33"/>
+      <c r="C24" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="14" t="s">
         <v>115</v>
       </c>
       <c r="G24" s="3" t="s">
@@ -2336,19 +2434,19 @@
       <c r="H24" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24" s="12">
         <v>3</v>
       </c>
       <c r="K24" s="12">
         <v>1200</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M24" s="39">
+      <c r="M24" s="26">
         <v>3.0500000000000002E-3</v>
       </c>
       <c r="N24" s="8">
@@ -2363,17 +2461,17 @@
       <c r="A25" s="13">
         <v>23</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="33" t="s">
+      <c r="B25" s="33"/>
+      <c r="C25" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="35" t="s">
+      <c r="D25" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="14" t="s">
         <v>118</v>
       </c>
       <c r="G25" s="3" t="s">
@@ -2382,19 +2480,19 @@
       <c r="H25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="35" t="s">
+      <c r="I25" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="J25" s="38">
+      <c r="J25" s="12">
         <v>3</v>
       </c>
       <c r="K25" s="12">
         <v>1200</v>
       </c>
-      <c r="L25" s="15" t="s">
+      <c r="L25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M25" s="39">
+      <c r="M25" s="26">
         <v>3.5999999999999999E-3</v>
       </c>
       <c r="N25" s="8">
@@ -2409,17 +2507,17 @@
       <c r="A26" s="13">
         <v>24</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="33" t="s">
+      <c r="B26" s="33"/>
+      <c r="C26" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="14" t="s">
         <v>121</v>
       </c>
       <c r="G26" s="3" t="s">
@@ -2428,19 +2526,19 @@
       <c r="H26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="35" t="s">
+      <c r="I26" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="12">
         <v>6</v>
       </c>
       <c r="K26" s="12">
         <v>2400</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M26" s="39">
+      <c r="M26" s="26">
         <v>4.3600000000000002E-3</v>
       </c>
       <c r="N26" s="8">
@@ -2455,17 +2553,17 @@
       <c r="A27" s="13">
         <v>25</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="33" t="s">
+      <c r="B27" s="33"/>
+      <c r="C27" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="35" t="s">
+      <c r="D27" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F27" s="14" t="s">
         <v>124</v>
       </c>
       <c r="G27" s="3" t="s">
@@ -2474,19 +2572,19 @@
       <c r="H27" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="35" t="s">
+      <c r="I27" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27" s="12">
         <v>1</v>
       </c>
       <c r="K27" s="12">
         <v>400</v>
       </c>
-      <c r="L27" s="15" t="s">
+      <c r="L27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="39">
+      <c r="M27" s="26">
         <v>6.7999999999999996E-3</v>
       </c>
       <c r="N27" s="8">
@@ -2497,39 +2595,47 @@
       <c r="P27" s="2"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13">
         <v>26</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="33" t="s">
+      <c r="B28" s="33"/>
+      <c r="C28" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="35" t="s">
+      <c r="D28" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="35" t="s">
+      <c r="G28" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="12">
         <v>2</v>
       </c>
       <c r="K28" s="12">
         <v>800</v>
       </c>
-      <c r="L28" s="6"/>
-      <c r="M28" s="39"/>
+      <c r="L28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="26">
+        <v>0.20032</v>
+      </c>
       <c r="N28" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160.256</v>
       </c>
       <c r="O28" s="4"/>
       <c r="P28" s="2"/>
@@ -2539,35 +2645,43 @@
       <c r="A29" s="13">
         <v>27</v>
       </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="33" t="s">
+      <c r="B29" s="33"/>
+      <c r="C29" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="35" t="s">
+      <c r="D29" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F29" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="35" t="s">
+      <c r="G29" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29" s="12">
         <v>1</v>
       </c>
       <c r="K29" s="12">
         <v>400</v>
       </c>
-      <c r="L29" s="6"/>
-      <c r="M29" s="39"/>
+      <c r="L29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="26">
+        <v>0.215</v>
+      </c>
       <c r="N29" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="O29" s="4"/>
       <c r="P29" s="2"/>
@@ -2577,32 +2691,32 @@
       <c r="A30" s="13">
         <v>28</v>
       </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="33" t="s">
+      <c r="B30" s="33"/>
+      <c r="C30" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="35" t="s">
+      <c r="F30" s="14" t="s">
         <v>134</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="35" t="s">
+      <c r="I30" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="12">
         <v>1</v>
       </c>
       <c r="K30" s="12">
         <v>400</v>
       </c>
       <c r="L30" s="6"/>
-      <c r="M30" s="39"/>
+      <c r="M30" s="26"/>
       <c r="N30" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2611,21 +2725,21 @@
       <c r="P30" s="2"/>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13">
         <v>29</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="33" t="s">
+      <c r="B31" s="34"/>
+      <c r="C31" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="35" t="s">
+      <c r="D31" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E31" s="35" t="s">
+      <c r="E31" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="35" t="s">
+      <c r="F31" s="14" t="s">
         <v>137</v>
       </c>
       <c r="G31" s="3" t="s">
@@ -2634,19 +2748,19 @@
       <c r="H31" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I31" s="35" t="s">
+      <c r="I31" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31" s="12">
         <v>8</v>
       </c>
       <c r="K31" s="5">
         <v>3200</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M31" s="39">
+      <c r="M31" s="26">
         <v>2.64E-3</v>
       </c>
       <c r="N31" s="8">
@@ -2661,28 +2775,32 @@
       <c r="A32" s="13">
         <v>30</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="D32" s="35" t="s">
+      <c r="D32" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35" t="s">
+      <c r="E32" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="14" t="s">
         <v>153</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
+      <c r="J32" s="3">
+        <v>1</v>
+      </c>
       <c r="K32" s="5">
         <v>400</v>
       </c>
       <c r="L32" s="6"/>
-      <c r="M32" s="4"/>
+      <c r="M32" s="26"/>
       <c r="N32" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2695,28 +2813,30 @@
       <c r="A33" s="13">
         <v>31</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D33" s="35" t="s">
+      <c r="D33" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35" t="s">
+      <c r="E33" s="14"/>
+      <c r="F33" s="14" t="s">
         <v>156</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
+      <c r="J33" s="3">
+        <v>1</v>
+      </c>
       <c r="K33" s="5">
         <v>900</v>
       </c>
       <c r="L33" s="6"/>
-      <c r="M33" s="4"/>
+      <c r="M33" s="26"/>
       <c r="N33" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2725,67 +2845,93 @@
       <c r="P33" s="2"/>
       <c r="Q33" s="2"/>
     </row>
-    <row r="34" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13">
         <v>32</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="33" t="s">
+      <c r="B34" s="33"/>
+      <c r="C34" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="D34" s="35" t="s">
+      <c r="D34" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35" t="s">
+      <c r="E34" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F34" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="37"/>
-      <c r="K34" s="36">
+      <c r="G34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J34" s="25">
+        <v>1</v>
+      </c>
+      <c r="K34" s="37">
         <v>400</v>
       </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="4"/>
+      <c r="L34" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" s="26">
+        <v>0.16800000000000001</v>
+      </c>
       <c r="N34" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.2</v>
       </c>
       <c r="O34" s="4"/>
       <c r="P34" s="2"/>
       <c r="Q34" s="2"/>
     </row>
-    <row r="35" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13">
         <v>33</v>
       </c>
-      <c r="B35" s="24"/>
-      <c r="C35" s="33" t="s">
+      <c r="B35" s="33"/>
+      <c r="C35" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="37"/>
-      <c r="K35" s="36">
+      <c r="G35" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J35" s="25">
+        <v>1</v>
+      </c>
+      <c r="K35" s="37">
         <v>400</v>
       </c>
-      <c r="L35" s="6"/>
-      <c r="M35" s="4"/>
+      <c r="L35" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M35" s="26">
+        <v>2.0099999999999998</v>
+      </c>
       <c r="N35" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>803.99999999999989</v>
       </c>
       <c r="O35" s="4"/>
       <c r="P35" s="2"/>
@@ -2795,127 +2941,169 @@
       <c r="A36" s="13">
         <v>34</v>
       </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="33" t="s">
+      <c r="B36" s="33"/>
+      <c r="C36" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="D36" s="35" t="s">
+      <c r="D36" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35" t="s">
+      <c r="E36" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F36" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="36">
+      <c r="G36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J36" s="25">
+        <v>1</v>
+      </c>
+      <c r="K36" s="37">
         <v>400</v>
       </c>
-      <c r="L36" s="6"/>
-      <c r="M36" s="4"/>
+      <c r="L36" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="M36" s="26">
+        <v>2.516</v>
+      </c>
       <c r="N36" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1006.4</v>
       </c>
       <c r="O36" s="4"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
-    <row r="37" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>35</v>
       </c>
-      <c r="B37" s="24"/>
-      <c r="C37" s="33" t="s">
+      <c r="B37" s="33"/>
+      <c r="C37" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="35" t="s">
+      <c r="D37" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35" t="s">
+      <c r="E37" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="36">
+      <c r="G37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J37" s="25">
+        <v>1</v>
+      </c>
+      <c r="K37" s="37">
         <v>400</v>
       </c>
-      <c r="L37" s="15"/>
-      <c r="M37" s="4"/>
+      <c r="L37" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="26">
+        <v>1.02328</v>
+      </c>
       <c r="N37" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>409.31200000000001</v>
       </c>
       <c r="O37" s="4"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
     </row>
-    <row r="38" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>36</v>
       </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="33" t="s">
+      <c r="B38" s="33"/>
+      <c r="C38" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="D38" s="35" t="s">
+      <c r="D38" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35" t="s">
+      <c r="E38" s="14"/>
+      <c r="F38" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="36">
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J38" s="25">
+        <v>1</v>
+      </c>
+      <c r="K38" s="37">
         <v>400</v>
       </c>
-      <c r="L38" s="6"/>
-      <c r="M38" s="4"/>
+      <c r="L38" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="M38" s="26">
+        <v>2.4500000000000002</v>
+      </c>
       <c r="N38" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>980.00000000000011</v>
       </c>
       <c r="O38" s="4"/>
       <c r="P38" s="2"/>
       <c r="Q38" s="2"/>
     </row>
-    <row r="39" spans="1:17" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13">
         <v>37</v>
       </c>
-      <c r="B39" s="25"/>
-      <c r="C39" s="33" t="s">
+      <c r="B39" s="34"/>
+      <c r="C39" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="35" t="s">
+      <c r="D39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35" t="s">
+      <c r="E39" s="14"/>
+      <c r="F39" s="14" t="s">
         <v>170</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="36">
+      <c r="J39" s="25">
+        <v>1</v>
+      </c>
+      <c r="K39" s="37">
         <v>400</v>
       </c>
       <c r="L39" s="6"/>
-      <c r="M39" s="4"/>
+      <c r="M39" s="26"/>
       <c r="N39" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O39" s="26"/>
+      <c r="O39" s="20"/>
       <c r="P39" s="2"/>
       <c r="Q39" s="2"/>
     </row>
@@ -2923,28 +3111,30 @@
       <c r="A40" s="13">
         <v>38</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="C40" s="30" t="s">
+      <c r="C40" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="D40" s="35" t="s">
+      <c r="D40" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35" t="s">
+      <c r="E40" s="14"/>
+      <c r="F40" s="14" t="s">
         <v>173</v>
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="36">
+      <c r="J40" s="25">
+        <v>1</v>
+      </c>
+      <c r="K40" s="37">
         <v>400</v>
       </c>
       <c r="L40" s="6"/>
-      <c r="M40" s="4"/>
+      <c r="M40" s="26"/>
       <c r="N40" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2953,67 +3143,81 @@
       <c r="P40" s="2"/>
       <c r="Q40" s="2"/>
     </row>
-    <row r="41" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13">
         <v>39</v>
       </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="30" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="D41" s="35" t="s">
+      <c r="D41" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35" t="s">
+      <c r="E41" s="14"/>
+      <c r="F41" s="14" t="s">
         <v>176</v>
       </c>
       <c r="G41" s="14"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="36">
+      <c r="J41" s="25">
+        <v>1</v>
+      </c>
+      <c r="K41" s="37">
         <v>400</v>
       </c>
       <c r="L41" s="6"/>
-      <c r="M41" s="4"/>
+      <c r="M41" s="26"/>
       <c r="N41" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O41" s="26"/>
+      <c r="O41" s="20"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
     </row>
-    <row r="42" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13">
         <v>40</v>
       </c>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30" t="s">
+      <c r="B42" s="23"/>
+      <c r="C42" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="F42" s="30" t="s">
+      <c r="F42" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="36">
+      <c r="G42" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J42" s="25">
+        <v>1</v>
+      </c>
+      <c r="K42" s="37">
         <v>400</v>
       </c>
-      <c r="L42" s="6"/>
-      <c r="M42" s="4"/>
+      <c r="L42" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="26">
+        <v>0.21579999999999999</v>
+      </c>
       <c r="N42" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>86.32</v>
       </c>
       <c r="O42" s="4"/>
       <c r="P42" s="2"/>
@@ -3023,98 +3227,122 @@
       <c r="A43" s="13">
         <v>42</v>
       </c>
-      <c r="B43" s="31" t="s">
+      <c r="B43" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="30" t="s">
+      <c r="C43" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D43" s="35" t="s">
+      <c r="D43" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="E43" s="30" t="s">
+      <c r="E43" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="F43" s="30" t="s">
+      <c r="F43" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
+      <c r="G43" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2</v>
+      </c>
       <c r="K43" s="5">
         <v>800</v>
       </c>
-      <c r="L43" s="6"/>
-      <c r="M43" s="4"/>
+      <c r="L43" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="4">
+        <v>0.27306000000000002</v>
+      </c>
       <c r="N43" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>218.44800000000001</v>
       </c>
       <c r="O43" s="4"/>
       <c r="P43" s="2"/>
       <c r="Q43" s="2"/>
     </row>
-    <row r="44" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>43</v>
       </c>
-      <c r="B44" s="32"/>
-      <c r="C44" s="30" t="s">
+      <c r="B44" s="28"/>
+      <c r="C44" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="E44" s="30" t="s">
+      <c r="E44" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="F44" s="30" t="s">
+      <c r="F44" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="3"/>
+      <c r="G44" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="H44" s="3">
+        <v>61300511121</v>
+      </c>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
+      <c r="J44" s="3">
+        <v>1</v>
+      </c>
       <c r="K44" s="5">
         <v>400</v>
       </c>
-      <c r="L44" s="6"/>
-      <c r="M44" s="4"/>
+      <c r="L44" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M44" s="26">
+        <v>0.26</v>
+      </c>
       <c r="N44" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="O44" s="4"/>
       <c r="P44" s="2"/>
       <c r="Q44" s="2"/>
     </row>
-    <row r="45" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="13">
         <v>44</v>
       </c>
-      <c r="B45" s="32"/>
-      <c r="C45" s="30" t="s">
+      <c r="B45" s="28"/>
+      <c r="C45" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="30" t="s">
+      <c r="E45" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="30" t="s">
+      <c r="F45" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
+      <c r="J45" s="3">
+        <v>7</v>
+      </c>
       <c r="K45" s="5">
         <v>2800</v>
       </c>
       <c r="L45" s="7"/>
-      <c r="M45" s="4"/>
+      <c r="M45" s="26"/>
       <c r="N45" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3127,28 +3355,30 @@
       <c r="A46" s="13">
         <v>45</v>
       </c>
-      <c r="B46" s="32"/>
-      <c r="C46" s="30" t="s">
+      <c r="B46" s="28"/>
+      <c r="C46" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="D46" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="E46" s="30" t="s">
+      <c r="E46" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="30" t="s">
+      <c r="F46" s="14" t="s">
         <v>41</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
+      <c r="J46" s="3">
+        <v>6</v>
+      </c>
       <c r="K46" s="5">
         <v>2400</v>
       </c>
       <c r="L46" s="7"/>
-      <c r="M46" s="4"/>
+      <c r="M46" s="26"/>
       <c r="N46" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -3159,8 +3389,6 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47"/>
-      <c r="E47"/>
-      <c r="F47"/>
       <c r="I47"/>
       <c r="J47"/>
       <c r="P47" s="2"/>
@@ -3168,8 +3396,6 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48"/>
-      <c r="E48"/>
-      <c r="F48"/>
       <c r="I48"/>
       <c r="J48"/>
       <c r="P48" s="2"/>
@@ -3177,8 +3403,6 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49"/>
-      <c r="E49"/>
-      <c r="F49"/>
       <c r="I49"/>
       <c r="J49"/>
       <c r="P49" s="2"/>
@@ -3186,8 +3410,6 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50"/>
-      <c r="E50"/>
-      <c r="F50"/>
       <c r="I50"/>
       <c r="J50"/>
       <c r="P50" s="2"/>
@@ -3195,8 +3417,6 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51"/>
-      <c r="E51"/>
-      <c r="F51"/>
       <c r="I51"/>
       <c r="J51"/>
       <c r="P51" s="2"/>
@@ -3204,8 +3424,6 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52"/>
-      <c r="E52"/>
-      <c r="F52"/>
       <c r="I52"/>
       <c r="J52"/>
       <c r="P52" s="2"/>
@@ -3213,8 +3431,6 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53"/>
-      <c r="E53"/>
-      <c r="F53"/>
       <c r="I53"/>
       <c r="J53"/>
       <c r="P53" s="2"/>
@@ -3222,8 +3438,6 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54"/>
-      <c r="E54"/>
-      <c r="F54"/>
       <c r="I54"/>
       <c r="J54"/>
       <c r="P54" s="2"/>
@@ -3231,8 +3445,6 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55"/>
-      <c r="E55"/>
-      <c r="F55"/>
       <c r="I55"/>
       <c r="J55"/>
       <c r="P55" s="2"/>
@@ -3240,8 +3452,6 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
-      <c r="E56"/>
-      <c r="F56"/>
       <c r="I56"/>
       <c r="J56"/>
       <c r="P56" s="2"/>
@@ -3249,8 +3459,6 @@
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
-      <c r="E57"/>
-      <c r="F57"/>
       <c r="I57"/>
       <c r="J57"/>
       <c r="P57" s="2"/>
@@ -3258,8 +3466,6 @@
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
-      <c r="E58"/>
-      <c r="F58"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="P58" s="2"/>
@@ -3267,8 +3473,6 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59"/>
-      <c r="E59"/>
-      <c r="F59"/>
       <c r="I59"/>
       <c r="J59"/>
       <c r="P59" s="2"/>
@@ -3276,8 +3480,6 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60"/>
-      <c r="E60"/>
-      <c r="F60"/>
       <c r="I60"/>
       <c r="J60"/>
       <c r="P60" s="2"/>
@@ -3285,29 +3487,21 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61"/>
-      <c r="E61"/>
-      <c r="F61"/>
       <c r="I61"/>
       <c r="J61"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62"/>
-      <c r="E62"/>
-      <c r="F62"/>
       <c r="I62"/>
       <c r="J62"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63"/>
-      <c r="E63"/>
-      <c r="F63"/>
       <c r="I63"/>
       <c r="J63"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64"/>
-      <c r="E64"/>
-      <c r="F64"/>
       <c r="I64"/>
       <c r="J64"/>
     </row>
@@ -3477,9 +3671,21 @@
     <hyperlink ref="L26" r:id="rId15"/>
     <hyperlink ref="L27" r:id="rId16"/>
     <hyperlink ref="L31" r:id="rId17"/>
+    <hyperlink ref="L28" r:id="rId18"/>
+    <hyperlink ref="L29" r:id="rId19"/>
+    <hyperlink ref="L34" r:id="rId20"/>
+    <hyperlink ref="L35" r:id="rId21"/>
+    <hyperlink ref="L36" r:id="rId22"/>
+    <hyperlink ref="L37" r:id="rId23"/>
+    <hyperlink ref="L38" r:id="rId24"/>
+    <hyperlink ref="L42" r:id="rId25"/>
+    <hyperlink ref="L43" r:id="rId26"/>
+    <hyperlink ref="L44" r:id="rId27"/>
+    <hyperlink ref="L19" r:id="rId28"/>
+    <hyperlink ref="L20" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId30"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
